--- a/alertas/alertas_2026-07-07.xlsx
+++ b/alertas/alertas_2026-07-07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="43">
   <si>
     <t>Fecha</t>
   </si>
@@ -31,25 +31,31 @@
     <t>Unidad</t>
   </si>
   <si>
+    <t>07/07/2026 04:14</t>
+  </si>
+  <si>
+    <t>heladera BM muestras</t>
+  </si>
+  <si>
+    <t>ambiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> °C</t>
+  </si>
+  <si>
+    <t>07/07/2026 04:10</t>
+  </si>
+  <si>
+    <t>heladera BM reactivos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ambiente </t>
+  </si>
+  <si>
     <t>07/07/2026 03:59</t>
   </si>
   <si>
-    <t>heladera BM muestras</t>
-  </si>
-  <si>
-    <t>ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> °C</t>
-  </si>
-  <si>
     <t>07/07/2026 03:54</t>
-  </si>
-  <si>
-    <t>heladera BM reactivos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ambiente </t>
   </si>
   <si>
     <t>07/07/2026 03:44</t>
@@ -510,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
@@ -648,10 +654,10 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>-15</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -659,13 +665,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E9">
         <v>26</v>
@@ -676,16 +682,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
       <c r="E10">
-        <v>26</v>
+        <v>-15</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -699,10 +705,10 @@
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>-15</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
@@ -713,10 +719,10 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12">
         <v>26</v>
@@ -730,13 +736,13 @@
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E13">
-        <v>26</v>
+        <v>-15</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -832,21 +838,21 @@
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
@@ -863,19 +869,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
         <v>34</v>
-      </c>
-      <c r="C21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21">
-        <v>26</v>
-      </c>
-      <c r="F21" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -900,10 +906,10 @@
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E23">
         <v>26</v>
@@ -917,13 +923,13 @@
         <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E24">
-        <v>-15</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
@@ -934,13 +940,13 @@
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
@@ -948,18 +954,52 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E26">
         <v>-15</v>
       </c>
       <c r="F26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28">
+        <v>-15</v>
+      </c>
+      <c r="F28" t="s">
         <v>9</v>
       </c>
     </row>

--- a/alertas/alertas_2026-07-07.xlsx
+++ b/alertas/alertas_2026-07-07.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="53">
   <si>
     <t>Fecha</t>
   </si>
@@ -31,27 +31,66 @@
     <t>Unidad</t>
   </si>
   <si>
+    <t>07/07/2026 05:30</t>
+  </si>
+  <si>
+    <t>heladera BM reactivos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ambiente </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> °C</t>
+  </si>
+  <si>
+    <t>07/07/2026 05:29</t>
+  </si>
+  <si>
+    <t>heladera BM muestras</t>
+  </si>
+  <si>
+    <t>ambiente</t>
+  </si>
+  <si>
+    <t>07/07/2026 05:14</t>
+  </si>
+  <si>
+    <t>07/07/2026 05:00</t>
+  </si>
+  <si>
+    <t>07/07/2026 04:58</t>
+  </si>
+  <si>
+    <t>07/07/2026 04:44</t>
+  </si>
+  <si>
+    <t>07/07/2026 04:43</t>
+  </si>
+  <si>
+    <t>07/07/2026 04:29</t>
+  </si>
+  <si>
+    <t>07/07/2026 04:26</t>
+  </si>
+  <si>
+    <t>07/07/2026 04:22</t>
+  </si>
+  <si>
+    <t>EL-356 Heladera</t>
+  </si>
+  <si>
+    <t>temp</t>
+  </si>
+  <si>
+    <t>min.</t>
+  </si>
+  <si>
     <t>07/07/2026 04:14</t>
   </si>
   <si>
-    <t>heladera BM muestras</t>
-  </si>
-  <si>
-    <t>ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> °C</t>
-  </si>
-  <si>
     <t>07/07/2026 04:10</t>
   </si>
   <si>
-    <t>heladera BM reactivos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ambiente </t>
-  </si>
-  <si>
     <t>07/07/2026 03:59</t>
   </si>
   <si>
@@ -112,12 +151,6 @@
     <t>EL-370 Heladera</t>
   </si>
   <si>
-    <t>temp</t>
-  </si>
-  <si>
-    <t>min.</t>
-  </si>
-  <si>
     <t>07/07/2026 01:59</t>
   </si>
   <si>
@@ -134,9 +167,6 @@
   </si>
   <si>
     <t>06/07/2026 18:54</t>
-  </si>
-  <si>
-    <t>EL-356 Heladera</t>
   </si>
   <si>
     <t>06/07/2026 18:51</t>
@@ -516,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
@@ -597,7 +627,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -614,13 +644,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>26</v>
@@ -631,13 +661,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>26</v>
@@ -648,13 +678,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E8">
         <v>26</v>
@@ -665,13 +695,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>26</v>
@@ -682,16 +712,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>-15</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -699,7 +729,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
@@ -716,36 +746,36 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
       <c r="E12">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
         <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13">
-        <v>-15</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -753,10 +783,10 @@
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E14">
         <v>26</v>
@@ -770,10 +800,10 @@
         <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>26</v>
@@ -787,10 +817,10 @@
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E16">
         <v>26</v>
@@ -804,10 +834,10 @@
         <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>26</v>
@@ -821,10 +851,10 @@
         <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E18">
         <v>26</v>
@@ -838,10 +868,10 @@
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>26</v>
@@ -855,10 +885,10 @@
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E20">
         <v>26</v>
@@ -872,30 +902,30 @@
         <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E22">
-        <v>26</v>
+        <v>-15</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
@@ -903,7 +933,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -920,7 +950,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
@@ -937,16 +967,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E25">
-        <v>26</v>
+        <v>-15</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
@@ -954,16 +984,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E26">
-        <v>-15</v>
+        <v>26</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
@@ -971,16 +1001,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
@@ -988,18 +1018,222 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28">
+        <v>26</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29">
+        <v>26</v>
+      </c>
+      <c r="F29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30">
+        <v>26</v>
+      </c>
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>42</v>
       </c>
-      <c r="C28" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28">
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31">
+        <v>26</v>
+      </c>
+      <c r="F31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32">
+        <v>26</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <v>26</v>
+      </c>
+      <c r="F34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35">
+        <v>26</v>
+      </c>
+      <c r="F35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36">
+        <v>26</v>
+      </c>
+      <c r="F36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>26</v>
+      </c>
+      <c r="F37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E38">
         <v>-15</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40">
+        <v>-15</v>
+      </c>
+      <c r="F40" t="s">
         <v>9</v>
       </c>
     </row>
